--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -2176,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118391340</v>
+        <v>118391308</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,31 +2188,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2256,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118391308</v>
+        <v>118391340</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,30 +2304,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -2176,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118391308</v>
+        <v>118391340</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,30 +2188,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2255,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118391340</v>
+        <v>118391308</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,31 +2305,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118395249</v>
+        <v>118394918</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2776,30 +2776,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2808,13 +2809,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585142</v>
+        <v>585210</v>
       </c>
       <c r="R20" t="n">
-        <v>7060158</v>
+        <v>7060103</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2843,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2853,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,22 +2869,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118395176</v>
+        <v>118394461</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2892,42 +2893,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585144</v>
+        <v>585561</v>
       </c>
       <c r="R21" t="n">
-        <v>7060155</v>
+        <v>7060076</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2959,7 +2956,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2969,7 +2966,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118394918</v>
+        <v>118395249</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3008,31 +3005,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3041,13 +3037,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585210</v>
+        <v>585142</v>
       </c>
       <c r="R22" t="n">
-        <v>7060103</v>
+        <v>7060158</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3076,7 +3072,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3086,7 +3082,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,22 +3097,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118394461</v>
+        <v>118395176</v>
       </c>
       <c r="B23" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3125,38 +3121,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585561</v>
+        <v>585144</v>
       </c>
       <c r="R23" t="n">
-        <v>7060076</v>
+        <v>7060155</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118394735</v>
+        <v>118394934</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1057,19 +1057,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585306</v>
+        <v>585194</v>
       </c>
       <c r="R5" t="n">
-        <v>7060139</v>
+        <v>7060084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118394810</v>
+        <v>118395113</v>
       </c>
       <c r="B7" t="n">
-        <v>100080</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,38 +1262,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585307</v>
+        <v>585159</v>
       </c>
       <c r="R7" t="n">
-        <v>7060149</v>
+        <v>7060159</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118395387</v>
+        <v>118394810</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>100080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,43 +1388,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585100</v>
+        <v>585307</v>
       </c>
       <c r="R8" t="n">
-        <v>7060200</v>
+        <v>7060149</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118395065</v>
+        <v>118391397</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1524,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585146</v>
+        <v>585264</v>
       </c>
       <c r="R9" t="n">
-        <v>7060152</v>
+        <v>7059904</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118394233</v>
+        <v>118395176</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,43 +1617,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585599</v>
+        <v>585144</v>
       </c>
       <c r="R10" t="n">
-        <v>7059910</v>
+        <v>7060155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1721,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118394406</v>
+        <v>118394663</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1758,13 +1766,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585555</v>
+        <v>585363</v>
       </c>
       <c r="R11" t="n">
-        <v>7059984</v>
+        <v>7060190</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,22 +1826,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118394890</v>
+        <v>118394722</v>
       </c>
       <c r="B12" t="n">
-        <v>100080</v>
+        <v>57290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1850,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585209</v>
+        <v>585307</v>
       </c>
       <c r="R12" t="n">
-        <v>7060118</v>
+        <v>7060157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,22 +1943,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118394546</v>
+        <v>118395249</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,46 +1967,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585501</v>
+        <v>585142</v>
       </c>
       <c r="R13" t="n">
-        <v>7060096</v>
+        <v>7060158</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2022,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,19 +2059,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118394466</v>
+        <v>118394233</v>
       </c>
       <c r="B14" t="n">
         <v>57290</v>
@@ -2095,7 +2107,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2104,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585532</v>
+        <v>585599</v>
       </c>
       <c r="R14" t="n">
-        <v>7060076</v>
+        <v>7059910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,19 +2176,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118391340</v>
+        <v>118394546</v>
       </c>
       <c r="B15" t="n">
         <v>57290</v>
@@ -2217,14 +2229,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585246</v>
+        <v>585501</v>
       </c>
       <c r="R15" t="n">
-        <v>7059953</v>
+        <v>7060096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2268,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2278,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,10 +2305,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118391308</v>
+        <v>118395194</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,30 +2317,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2337,13 +2350,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585246</v>
+        <v>585141</v>
       </c>
       <c r="R16" t="n">
-        <v>7059953</v>
+        <v>7060147</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,7 +2385,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2395,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2410,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118394266</v>
+        <v>118394735</v>
       </c>
       <c r="B17" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,37 +2438,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585590</v>
+        <v>585306</v>
       </c>
       <c r="R17" t="n">
-        <v>7059919</v>
+        <v>7060139</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,19 +2527,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118395113</v>
+        <v>118391340</v>
       </c>
       <c r="B18" t="n">
         <v>57290</v>
@@ -2554,19 +2572,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2575,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585159</v>
+        <v>585246</v>
       </c>
       <c r="R18" t="n">
-        <v>7060159</v>
+        <v>7059953</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2620,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,7 +2656,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118395194</v>
+        <v>118394466</v>
       </c>
       <c r="B19" t="n">
         <v>57290</v>
@@ -2683,22 +2692,22 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585141</v>
+        <v>585532</v>
       </c>
       <c r="R19" t="n">
-        <v>7060147</v>
+        <v>7060076</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2727,7 +2736,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2737,7 +2746,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2764,7 +2773,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118394918</v>
+        <v>118394406</v>
       </c>
       <c r="B20" t="n">
         <v>57290</v>
@@ -2800,22 +2809,22 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585210</v>
+        <v>585555</v>
       </c>
       <c r="R20" t="n">
-        <v>7060103</v>
+        <v>7059984</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2844,7 +2853,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2863,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,12 +2878,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2993,10 +3002,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118395249</v>
+        <v>118395387</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,30 +3014,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3037,13 +3047,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585142</v>
+        <v>585100</v>
       </c>
       <c r="R22" t="n">
-        <v>7060158</v>
+        <v>7060200</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3072,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3082,7 +3092,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,22 +3107,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118395176</v>
+        <v>118394890</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>100080</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,42 +3131,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585144</v>
+        <v>585209</v>
       </c>
       <c r="R23" t="n">
-        <v>7060155</v>
+        <v>7060118</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,7 +3194,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3198,7 +3204,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118391397</v>
+        <v>118391308</v>
       </c>
       <c r="B24" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,31 +3243,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3270,10 +3275,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585264</v>
+        <v>585246</v>
       </c>
       <c r="R24" t="n">
-        <v>7059904</v>
+        <v>7059953</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3310,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3320,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,10 +3347,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118394722</v>
+        <v>118394266</v>
       </c>
       <c r="B25" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,42 +3363,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585307</v>
+        <v>585590</v>
       </c>
       <c r="R25" t="n">
-        <v>7060157</v>
+        <v>7059919</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,7 +3459,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394663</v>
+        <v>118394918</v>
       </c>
       <c r="B26" t="n">
         <v>57290</v>
@@ -3495,19 +3495,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585363</v>
+        <v>585210</v>
       </c>
       <c r="R26" t="n">
-        <v>7060190</v>
+        <v>7060103</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3576,7 +3576,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118394934</v>
+        <v>118395065</v>
       </c>
       <c r="B27" t="n">
         <v>57290</v>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585194</v>
+        <v>585146</v>
       </c>
       <c r="R27" t="n">
-        <v>7060084</v>
+        <v>7060152</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3347,10 +3347,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118394266</v>
+        <v>118394918</v>
       </c>
       <c r="B25" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3363,37 +3363,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585590</v>
+        <v>585210</v>
       </c>
       <c r="R25" t="n">
-        <v>7059919</v>
+        <v>7060103</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3422,7 +3427,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3432,7 +3437,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,19 +3452,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394918</v>
+        <v>118395065</v>
       </c>
       <c r="B26" t="n">
         <v>57290</v>
@@ -3504,10 +3509,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585210</v>
+        <v>585146</v>
       </c>
       <c r="R26" t="n">
-        <v>7060103</v>
+        <v>7060152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,7 +3544,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3549,7 +3554,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3576,10 +3581,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118395065</v>
+        <v>118394266</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3592,42 +3597,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585146</v>
+        <v>585590</v>
       </c>
       <c r="R27" t="n">
-        <v>7060152</v>
+        <v>7059919</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,12 +3681,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118394934</v>
+        <v>118394918</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585194</v>
+        <v>585210</v>
       </c>
       <c r="R5" t="n">
-        <v>7060084</v>
+        <v>7060103</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118394828</v>
+        <v>118394233</v>
       </c>
       <c r="B6" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585266</v>
+        <v>585599</v>
       </c>
       <c r="R6" t="n">
-        <v>7060133</v>
+        <v>7059910</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1243,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1376,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118394810</v>
+        <v>118394406</v>
       </c>
       <c r="B8" t="n">
-        <v>100080</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,41 +1393,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585307</v>
+        <v>585555</v>
       </c>
       <c r="R8" t="n">
-        <v>7060149</v>
+        <v>7059984</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,19 +1486,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118391397</v>
+        <v>118394934</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1533,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585264</v>
+        <v>585194</v>
       </c>
       <c r="R9" t="n">
-        <v>7059904</v>
+        <v>7060084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118394663</v>
+        <v>118394466</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1766,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585363</v>
+        <v>585532</v>
       </c>
       <c r="R11" t="n">
-        <v>7060190</v>
+        <v>7060076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,7 +1821,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,19 +1836,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118394722</v>
+        <v>118395065</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1879,14 +1889,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585307</v>
+        <v>585146</v>
       </c>
       <c r="R12" t="n">
-        <v>7060157</v>
+        <v>7060152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,22 +1953,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118395249</v>
+        <v>118394461</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,45 +1977,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585142</v>
+        <v>585561</v>
       </c>
       <c r="R13" t="n">
-        <v>7060158</v>
+        <v>7060076</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2050,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,22 +2065,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118394233</v>
+        <v>118394266</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,42 +2093,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585599</v>
+        <v>585590</v>
       </c>
       <c r="R14" t="n">
-        <v>7059910</v>
+        <v>7059919</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2151,7 +2152,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2162,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,19 +2177,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118394546</v>
+        <v>118391397</v>
       </c>
       <c r="B15" t="n">
         <v>57290</v>
@@ -2224,19 +2225,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585501</v>
+        <v>585264</v>
       </c>
       <c r="R15" t="n">
-        <v>7060096</v>
+        <v>7059904</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2278,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,7 +2306,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118395194</v>
+        <v>118395387</v>
       </c>
       <c r="B16" t="n">
         <v>57290</v>
@@ -2350,13 +2351,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585141</v>
+        <v>585100</v>
       </c>
       <c r="R16" t="n">
-        <v>7060147</v>
+        <v>7060200</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2385,7 +2386,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2395,7 +2396,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,22 +2411,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118394735</v>
+        <v>118395249</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,46 +2435,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585306</v>
+        <v>585142</v>
       </c>
       <c r="R17" t="n">
-        <v>7060139</v>
+        <v>7060158</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,12 +2527,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118394466</v>
+        <v>118394810</v>
       </c>
       <c r="B19" t="n">
-        <v>57290</v>
+        <v>100080</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2668,43 +2668,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585532</v>
+        <v>585307</v>
       </c>
       <c r="R19" t="n">
-        <v>7060076</v>
+        <v>7060149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2736,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2746,7 +2741,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,19 +2756,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118394406</v>
+        <v>118395194</v>
       </c>
       <c r="B20" t="n">
         <v>57290</v>
@@ -2809,19 +2804,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585555</v>
+        <v>585141</v>
       </c>
       <c r="R20" t="n">
-        <v>7059984</v>
+        <v>7060147</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2853,7 +2848,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2863,7 +2858,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,10 +2885,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118394461</v>
+        <v>118394722</v>
       </c>
       <c r="B21" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2906,34 +2901,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585561</v>
+        <v>585307</v>
       </c>
       <c r="R21" t="n">
-        <v>7060076</v>
+        <v>7060157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,22 +2990,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118395387</v>
+        <v>118391308</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3014,31 +3014,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3047,10 +3046,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585100</v>
+        <v>585246</v>
       </c>
       <c r="R22" t="n">
-        <v>7060200</v>
+        <v>7059953</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3082,7 +3081,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +3091,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3231,10 +3230,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118391308</v>
+        <v>118394735</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3243,42 +3242,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585246</v>
+        <v>585306</v>
       </c>
       <c r="R24" t="n">
-        <v>7059953</v>
+        <v>7060139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,7 +3347,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118394918</v>
+        <v>118394663</v>
       </c>
       <c r="B25" t="n">
         <v>57290</v>
@@ -3383,19 +3383,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585210</v>
+        <v>585363</v>
       </c>
       <c r="R25" t="n">
-        <v>7060103</v>
+        <v>7060190</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118395065</v>
+        <v>118394828</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,39 +3480,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585146</v>
+        <v>585266</v>
       </c>
       <c r="R26" t="n">
-        <v>7060152</v>
+        <v>7060133</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3544,7 +3539,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3554,7 +3549,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,22 +3564,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118394266</v>
+        <v>118394546</v>
       </c>
       <c r="B27" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3597,37 +3592,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585590</v>
+        <v>585501</v>
       </c>
       <c r="R27" t="n">
-        <v>7059919</v>
+        <v>7060096</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,12 +3681,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118394918</v>
+        <v>118391397</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585210</v>
+        <v>585264</v>
       </c>
       <c r="R5" t="n">
-        <v>7060103</v>
+        <v>7059904</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118394233</v>
+        <v>118394466</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1174,7 +1174,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585599</v>
+        <v>585532</v>
       </c>
       <c r="R6" t="n">
-        <v>7059910</v>
+        <v>7060076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,19 +1243,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118395113</v>
+        <v>118395065</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1288,19 +1288,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1309,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585159</v>
+        <v>585146</v>
       </c>
       <c r="R7" t="n">
-        <v>7060159</v>
+        <v>7060152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118394406</v>
+        <v>118394546</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1426,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585555</v>
+        <v>585501</v>
       </c>
       <c r="R8" t="n">
-        <v>7059984</v>
+        <v>7060096</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,12 +1477,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1615,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118395176</v>
+        <v>118394890</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>100087</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,42 +1618,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585144</v>
+        <v>585209</v>
       </c>
       <c r="R10" t="n">
-        <v>7060155</v>
+        <v>7060118</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118394466</v>
+        <v>118394828</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>90507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585532</v>
+        <v>585266</v>
       </c>
       <c r="R11" t="n">
-        <v>7060076</v>
+        <v>7060133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,7 +1830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118395065</v>
+        <v>118395387</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1893,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585146</v>
+        <v>585100</v>
       </c>
       <c r="R12" t="n">
-        <v>7060152</v>
+        <v>7060200</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118394461</v>
+        <v>118394810</v>
       </c>
       <c r="B13" t="n">
-        <v>90522</v>
+        <v>100087</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,25 +1959,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2005,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585561</v>
+        <v>585307</v>
       </c>
       <c r="R13" t="n">
-        <v>7060076</v>
+        <v>7060149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2050,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118394266</v>
+        <v>118394233</v>
       </c>
       <c r="B14" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,37 +2075,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585590</v>
+        <v>585599</v>
       </c>
       <c r="R14" t="n">
-        <v>7059919</v>
+        <v>7059910</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2152,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2162,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118391397</v>
+        <v>118395176</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,31 +2188,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2234,10 +2220,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585264</v>
+        <v>585144</v>
       </c>
       <c r="R15" t="n">
-        <v>7059904</v>
+        <v>7060155</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,7 +2292,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118395387</v>
+        <v>118394663</v>
       </c>
       <c r="B16" t="n">
         <v>57290</v>
@@ -2342,19 +2328,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585100</v>
+        <v>585363</v>
       </c>
       <c r="R16" t="n">
-        <v>7060200</v>
+        <v>7060190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2386,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2396,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118395249</v>
+        <v>118395113</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,30 +2421,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2467,13 +2463,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585142</v>
+        <v>585159</v>
       </c>
       <c r="R17" t="n">
-        <v>7060158</v>
+        <v>7060159</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2502,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2512,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,12 +2523,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2656,10 +2652,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118394810</v>
+        <v>118394266</v>
       </c>
       <c r="B19" t="n">
-        <v>100080</v>
+        <v>90507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2668,25 +2664,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1365</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2696,13 +2692,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585307</v>
+        <v>585590</v>
       </c>
       <c r="R19" t="n">
-        <v>7060149</v>
+        <v>7059919</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2731,7 +2727,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2741,7 +2737,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,12 +2752,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2885,7 +2881,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118394722</v>
+        <v>118394735</v>
       </c>
       <c r="B21" t="n">
         <v>57290</v>
@@ -2921,7 +2917,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2930,10 +2926,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585307</v>
+        <v>585306</v>
       </c>
       <c r="R21" t="n">
-        <v>7060157</v>
+        <v>7060139</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2965,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2975,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,22 +2986,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118391308</v>
+        <v>118394406</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3014,45 +3010,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585246</v>
+        <v>585555</v>
       </c>
       <c r="R22" t="n">
-        <v>7059953</v>
+        <v>7059984</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3081,7 +3078,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3091,7 +3088,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,22 +3103,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118394890</v>
+        <v>118394722</v>
       </c>
       <c r="B23" t="n">
-        <v>100080</v>
+        <v>57290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,38 +3127,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585209</v>
+        <v>585307</v>
       </c>
       <c r="R23" t="n">
-        <v>7060118</v>
+        <v>7060157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3193,7 +3195,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3203,7 +3205,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,22 +3220,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118394735</v>
+        <v>118395249</v>
       </c>
       <c r="B24" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3242,46 +3244,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585306</v>
+        <v>585142</v>
       </c>
       <c r="R24" t="n">
-        <v>7060139</v>
+        <v>7060158</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3310,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3320,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,22 +3336,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118394663</v>
+        <v>118394461</v>
       </c>
       <c r="B25" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3363,39 +3364,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585363</v>
+        <v>585561</v>
       </c>
       <c r="R25" t="n">
-        <v>7060190</v>
+        <v>7060076</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3427,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3437,7 +3433,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3464,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394828</v>
+        <v>118391308</v>
       </c>
       <c r="B26" t="n">
-        <v>90500</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,38 +3472,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585266</v>
+        <v>585246</v>
       </c>
       <c r="R26" t="n">
-        <v>7060133</v>
+        <v>7059953</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,19 +3564,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118394546</v>
+        <v>118394918</v>
       </c>
       <c r="B27" t="n">
         <v>57290</v>
@@ -3612,19 +3612,19 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585501</v>
+        <v>585210</v>
       </c>
       <c r="R27" t="n">
-        <v>7060096</v>
+        <v>7060103</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118394266</v>
+        <v>118395194</v>
       </c>
       <c r="B19" t="n">
-        <v>90507</v>
+        <v>57290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2668,34 +2668,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585590</v>
+        <v>585141</v>
       </c>
       <c r="R19" t="n">
-        <v>7059919</v>
+        <v>7060147</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2727,7 +2732,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2737,7 +2742,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2764,10 +2769,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118395194</v>
+        <v>118394266</v>
       </c>
       <c r="B20" t="n">
-        <v>57290</v>
+        <v>90507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2780,39 +2785,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585141</v>
+        <v>585590</v>
       </c>
       <c r="R20" t="n">
-        <v>7060147</v>
+        <v>7059919</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118391397</v>
+        <v>118395194</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585264</v>
+        <v>585141</v>
       </c>
       <c r="R5" t="n">
-        <v>7059904</v>
+        <v>7060147</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,19 +1126,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118394466</v>
+        <v>118395387</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1174,19 +1174,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585532</v>
+        <v>585100</v>
       </c>
       <c r="R6" t="n">
-        <v>7060076</v>
+        <v>7060200</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,19 +1243,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118395065</v>
+        <v>118394722</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1296,14 +1296,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585146</v>
+        <v>585307</v>
       </c>
       <c r="R7" t="n">
-        <v>7060152</v>
+        <v>7060157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118394546</v>
+        <v>118394461</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585501</v>
+        <v>585561</v>
       </c>
       <c r="R8" t="n">
-        <v>7060096</v>
+        <v>7060076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118394934</v>
+        <v>118394663</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1525,19 +1520,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585194</v>
+        <v>585363</v>
       </c>
       <c r="R9" t="n">
-        <v>7060084</v>
+        <v>7060190</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118394890</v>
+        <v>118395249</v>
       </c>
       <c r="B10" t="n">
-        <v>100087</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,41 +1613,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585209</v>
+        <v>585142</v>
       </c>
       <c r="R10" t="n">
-        <v>7060118</v>
+        <v>7060158</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1705,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118394828</v>
+        <v>118394890</v>
       </c>
       <c r="B11" t="n">
-        <v>90507</v>
+        <v>100087</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,25 +1729,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585266</v>
+        <v>585209</v>
       </c>
       <c r="R11" t="n">
-        <v>7060133</v>
+        <v>7060118</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,19 +1817,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118395387</v>
+        <v>118391397</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1875,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585100</v>
+        <v>585264</v>
       </c>
       <c r="R12" t="n">
-        <v>7060200</v>
+        <v>7059904</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118394810</v>
+        <v>118394546</v>
       </c>
       <c r="B13" t="n">
-        <v>100087</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,38 +1958,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585307</v>
+        <v>585501</v>
       </c>
       <c r="R13" t="n">
-        <v>7060149</v>
+        <v>7060096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118394233</v>
+        <v>118395113</v>
       </c>
       <c r="B14" t="n">
         <v>57290</v>
@@ -2092,22 +2096,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585599</v>
+        <v>585159</v>
       </c>
       <c r="R14" t="n">
-        <v>7059910</v>
+        <v>7060159</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2152,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2162,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,10 +2189,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118395176</v>
+        <v>118395065</v>
       </c>
       <c r="B15" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,30 +2201,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2220,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585144</v>
+        <v>585146</v>
       </c>
       <c r="R15" t="n">
-        <v>7060155</v>
+        <v>7060152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118394663</v>
+        <v>118394810</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>100087</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,43 +2318,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585363</v>
+        <v>585307</v>
       </c>
       <c r="R16" t="n">
-        <v>7060190</v>
+        <v>7060149</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118395113</v>
+        <v>118394828</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>90507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,48 +2434,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585159</v>
+        <v>585266</v>
       </c>
       <c r="R17" t="n">
-        <v>7060159</v>
+        <v>7060133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,19 +2518,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118391340</v>
+        <v>118394934</v>
       </c>
       <c r="B18" t="n">
         <v>57290</v>
@@ -2571,7 +2566,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585246</v>
+        <v>585194</v>
       </c>
       <c r="R18" t="n">
-        <v>7059953</v>
+        <v>7060084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2615,7 +2610,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2625,7 +2620,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,7 +2647,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118395194</v>
+        <v>118391340</v>
       </c>
       <c r="B19" t="n">
         <v>57290</v>
@@ -2688,7 +2683,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2697,13 +2692,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585141</v>
+        <v>585246</v>
       </c>
       <c r="R19" t="n">
-        <v>7060147</v>
+        <v>7059953</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2732,7 +2727,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2742,7 +2737,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,22 +2752,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118394266</v>
+        <v>118394918</v>
       </c>
       <c r="B20" t="n">
-        <v>90507</v>
+        <v>57290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2785,37 +2780,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585590</v>
+        <v>585210</v>
       </c>
       <c r="R20" t="n">
-        <v>7059919</v>
+        <v>7060103</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,19 +2869,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118394735</v>
+        <v>118394406</v>
       </c>
       <c r="B21" t="n">
         <v>57290</v>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585306</v>
+        <v>585555</v>
       </c>
       <c r="R21" t="n">
-        <v>7060139</v>
+        <v>7059984</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,19 +2986,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118394406</v>
+        <v>118394233</v>
       </c>
       <c r="B22" t="n">
         <v>57290</v>
@@ -3034,7 +3034,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585555</v>
+        <v>585599</v>
       </c>
       <c r="R22" t="n">
-        <v>7059984</v>
+        <v>7059910</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,22 +3103,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118394722</v>
+        <v>118394266</v>
       </c>
       <c r="B23" t="n">
-        <v>57290</v>
+        <v>90507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3131,42 +3131,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585307</v>
+        <v>585590</v>
       </c>
       <c r="R23" t="n">
-        <v>7060157</v>
+        <v>7059919</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3195,7 +3190,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3205,7 +3200,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,7 +3227,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118395249</v>
+        <v>118395176</v>
       </c>
       <c r="B24" t="n">
         <v>97853</v>
@@ -3267,7 +3262,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3276,13 +3271,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585142</v>
+        <v>585144</v>
       </c>
       <c r="R24" t="n">
-        <v>7060158</v>
+        <v>7060155</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3311,7 +3306,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,7 +3316,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,22 +3331,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118394461</v>
+        <v>118391308</v>
       </c>
       <c r="B25" t="n">
-        <v>90529</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3360,38 +3355,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585561</v>
+        <v>585246</v>
       </c>
       <c r="R25" t="n">
-        <v>7060076</v>
+        <v>7059953</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3423,7 +3422,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,7 +3432,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3460,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118391308</v>
+        <v>118394466</v>
       </c>
       <c r="B26" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,42 +3471,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585246</v>
+        <v>585532</v>
       </c>
       <c r="R26" t="n">
-        <v>7059953</v>
+        <v>7060076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,19 +3564,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118394918</v>
+        <v>118394735</v>
       </c>
       <c r="B27" t="n">
         <v>57290</v>
@@ -3612,19 +3612,19 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585210</v>
+        <v>585306</v>
       </c>
       <c r="R27" t="n">
-        <v>7060103</v>
+        <v>7060139</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3691,6 +3691,117 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122246450</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100388</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>585307</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7060150</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Y-Sol-0421</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100388</v>
+        <v>100396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100396</v>
+        <v>100398</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100414</v>
+        <v>100424</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,11 +3696,11 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100424</v>
+        <v>100436</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100436</v>
+        <v>100441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,11 +3710,6 @@
       </c>
       <c r="E28" t="n">
         <v>1365</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100450</v>
+        <v>100463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,6 +3710,11 @@
       </c>
       <c r="E28" t="n">
         <v>1365</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100463</v>
+        <v>100476</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100476</v>
+        <v>100479</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100479</v>
+        <v>100480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100480</v>
+        <v>100483</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Y-Sol-0421</t>
+          <t>Y-Sol-0111</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3696,7 +3696,7 @@
         <v>122246450</v>
       </c>
       <c r="B28" t="n">
-        <v>100586</v>
+        <v>100594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3802,6 +3802,398 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126057619</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96460</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>585221</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7059982</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126055756</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91224</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>585572</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7059945</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126059319</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>585128</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7060135</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126057693</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>585221</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7059982</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96460</v>
+        <v>96464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126055756</v>
       </c>
       <c r="B30" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96464</v>
+        <v>96465</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126055756</v>
       </c>
       <c r="B30" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>126059319</v>
       </c>
       <c r="B31" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126055756</v>
       </c>
       <c r="B30" t="n">
-        <v>91230</v>
+        <v>91232</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96469</v>
+        <v>96471</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126055756</v>
       </c>
       <c r="B30" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126055756</v>
       </c>
       <c r="B30" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>126059319</v>
       </c>
       <c r="B31" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -3807,7 +3807,7 @@
         <v>126057619</v>
       </c>
       <c r="B29" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126055756</v>
       </c>
       <c r="B30" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>126059319</v>
       </c>
       <c r="B31" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126057693</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -4199,7 +4199,7 @@
         <v>131085086</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -4199,7 +4199,7 @@
         <v>131085086</v>
       </c>
       <c r="B33" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -4199,7 +4199,7 @@
         <v>131085086</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 29250-2024 artfynd.xlsx
+++ b/artfynd/A 29250-2024 artfynd.xlsx
@@ -4199,7 +4199,7 @@
         <v>131085086</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
